--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,6 +1020,3304 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128494294</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549270</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7132074</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128494276</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549393</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7132310</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack, ganska färska</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128494278</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>549169</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7132171</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128494289</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>549388</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7132402</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128494282</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>549266</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7132443</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128494290</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>549409</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7132455</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128494295</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>549282</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7132002</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128494267</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>549449</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7132243</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128494292</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>549349</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7132368</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128494268</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>549327</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7132397</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128494285</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>549438</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7132438</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128494300</v>
+      </c>
+      <c r="B16" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>510</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>549429</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7132363</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128494277</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91656</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>549287</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7132486</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128494286</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>549350</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7132364</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128494299</v>
+      </c>
+      <c r="B19" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>510</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>549452</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7132213</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128494274</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>549300</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7132514</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128494270</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>549423</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7132236</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128494266</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>549449</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7132219</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128494269</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>549355</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7132343</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128494301</v>
+      </c>
+      <c r="B24" t="n">
+        <v>88761</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>510</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>549427</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7132215</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128494281</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91356</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>549420</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7132412</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128494263</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>549306</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7131940</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128494261</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91360</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>549301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7132504</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128494291</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>549291</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7132495</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128494275</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>549391</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7132312</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Hack, ganska färska</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128494287</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>549058</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7132030</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128494296</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>549291</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7131952</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128494262</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91360</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>549277</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7132488</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128494288</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>549222</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7132132</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128494280</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57777</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>549368</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7132332</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128494293</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>549367</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7132331</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128494279</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80135</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>549323</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7131958</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128494284</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91378</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Frostberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>548999</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7132123</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128494294</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128494276</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>128494278</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128494289</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B9" t="n">
-        <v>91356</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R9" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R10" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,11 +1599,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
         <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>128494267</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>128494292</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>128494268</v>
       </c>
       <c r="B14" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128494285</v>
       </c>
       <c r="B15" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128494300</v>
       </c>
       <c r="B16" t="n">
-        <v>88761</v>
+        <v>88853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>91656</v>
+        <v>91748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494286</v>
+        <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>91378</v>
+        <v>88853</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549350</v>
+        <v>549452</v>
       </c>
       <c r="R18" t="n">
-        <v>7132364</v>
+        <v>7132213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494299</v>
+        <v>128494274</v>
       </c>
       <c r="B19" t="n">
-        <v>88761</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,22 +2456,22 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549452</v>
+        <v>549300</v>
       </c>
       <c r="R19" t="n">
-        <v>7132213</v>
+        <v>7132514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2492,6 +2492,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494274</v>
+        <v>128494286</v>
       </c>
       <c r="B20" t="n">
-        <v>57670</v>
+        <v>91470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2534,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549300</v>
+        <v>549350</v>
       </c>
       <c r="R20" t="n">
-        <v>7132514</v>
+        <v>7132364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2589,11 +2594,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,7 +2623,7 @@
         <v>128494270</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>128494266</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>128494269</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494301</v>
+        <v>128494263</v>
       </c>
       <c r="B24" t="n">
-        <v>88761</v>
+        <v>92149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549427</v>
+        <v>549306</v>
       </c>
       <c r="R24" t="n">
-        <v>7132215</v>
+        <v>7131940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128494281</v>
+        <v>128494301</v>
       </c>
       <c r="B25" t="n">
-        <v>91356</v>
+        <v>88853</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549420</v>
+        <v>549427</v>
       </c>
       <c r="R25" t="n">
-        <v>7132412</v>
+        <v>7132215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,32 +3120,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494263</v>
+        <v>128494281</v>
       </c>
       <c r="B26" t="n">
-        <v>92057</v>
+        <v>91448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549306</v>
+        <v>549420</v>
       </c>
       <c r="R26" t="n">
-        <v>7131940</v>
+        <v>7132412</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>128494261</v>
       </c>
       <c r="B27" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494291</v>
+        <v>128494287</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>91470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549291</v>
+        <v>549058</v>
       </c>
       <c r="R28" t="n">
-        <v>7132495</v>
+        <v>7132030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,11 +3385,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3416,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494275</v>
+        <v>128494291</v>
       </c>
       <c r="B29" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3422,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549391</v>
+        <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7132312</v>
+        <v>7132495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,7 +3486,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hack, ganska färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494287</v>
+        <v>128494296</v>
       </c>
       <c r="B30" t="n">
-        <v>91378</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R30" t="n">
-        <v>7132030</v>
+        <v>7131952</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,6 +3584,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R31" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128494262</v>
+        <v>128494288</v>
       </c>
       <c r="B32" t="n">
-        <v>91360</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549277</v>
+        <v>549222</v>
       </c>
       <c r="R32" t="n">
-        <v>7132488</v>
+        <v>7132132</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,6 +3788,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,10 +3819,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494288</v>
+        <v>128494293</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549222</v>
+        <v>549367</v>
       </c>
       <c r="R33" t="n">
-        <v>7132132</v>
+        <v>7132331</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,7 +3924,7 @@
         <v>128494280</v>
       </c>
       <c r="B34" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,10 +4030,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494293</v>
+        <v>128494262</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>91452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,21 +4041,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4060,10 +4065,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549367</v>
+        <v>549277</v>
       </c>
       <c r="R35" t="n">
-        <v>7132331</v>
+        <v>7132488</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,11 +4101,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4130,7 +4130,7 @@
         <v>128494279</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>91448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R9" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,11 +1497,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R10" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,6 +1594,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494285</v>
+        <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>91470</v>
+        <v>88853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549438</v>
+        <v>549429</v>
       </c>
       <c r="R15" t="n">
-        <v>7132438</v>
+        <v>7132363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494300</v>
+        <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>88853</v>
+        <v>91470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549429</v>
+        <v>549438</v>
       </c>
       <c r="R16" t="n">
-        <v>7132363</v>
+        <v>7132438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494274</v>
+        <v>128494286</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>91470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549300</v>
+        <v>549350</v>
       </c>
       <c r="R19" t="n">
-        <v>7132514</v>
+        <v>7132364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494286</v>
+        <v>128494270</v>
       </c>
       <c r="B20" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549350</v>
+        <v>549423</v>
       </c>
       <c r="R20" t="n">
-        <v>7132364</v>
+        <v>7132236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,6 +2589,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494270</v>
+        <v>128494274</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549423</v>
+        <v>549300</v>
       </c>
       <c r="R21" t="n">
-        <v>7132236</v>
+        <v>7132514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494266</v>
+        <v>128494269</v>
       </c>
       <c r="B22" t="n">
         <v>57685</v>
@@ -2757,22 +2757,22 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549449</v>
+        <v>549355</v>
       </c>
       <c r="R22" t="n">
-        <v>7132219</v>
+        <v>7132343</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,7 +2824,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494269</v>
+        <v>128494266</v>
       </c>
       <c r="B23" t="n">
         <v>57685</v>
@@ -2859,22 +2859,22 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549355</v>
+        <v>549449</v>
       </c>
       <c r="R23" t="n">
-        <v>7132343</v>
+        <v>7132219</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494263</v>
+        <v>128494261</v>
       </c>
       <c r="B24" t="n">
-        <v>92149</v>
+        <v>91452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549306</v>
+        <v>549301</v>
       </c>
       <c r="R24" t="n">
-        <v>7131940</v>
+        <v>7132504</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128494261</v>
+        <v>128494263</v>
       </c>
       <c r="B27" t="n">
-        <v>91452</v>
+        <v>92149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549301</v>
+        <v>549306</v>
       </c>
       <c r="R27" t="n">
-        <v>7132504</v>
+        <v>7131940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494287</v>
+        <v>128494291</v>
       </c>
       <c r="B28" t="n">
-        <v>91470</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R28" t="n">
-        <v>7132030</v>
+        <v>7132495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,6 +3385,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,7 +3416,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494291</v>
+        <v>128494296</v>
       </c>
       <c r="B29" t="n">
         <v>79083</v>
@@ -3449,7 +3454,7 @@
         <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7132495</v>
+        <v>7131952</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R30" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,7 +3593,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3615,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494275</v>
+        <v>128494287</v>
       </c>
       <c r="B31" t="n">
-        <v>57682</v>
+        <v>91470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3631,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549391</v>
+        <v>549058</v>
       </c>
       <c r="R31" t="n">
-        <v>7132312</v>
+        <v>7132030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3921,57 +3921,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494280</v>
+        <v>128494262</v>
       </c>
       <c r="B34" t="n">
-        <v>57789</v>
+        <v>91452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549368</v>
+        <v>549277</v>
       </c>
       <c r="R34" t="n">
-        <v>7132332</v>
+        <v>7132488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4030,45 +4018,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494262</v>
+        <v>128494280</v>
       </c>
       <c r="B35" t="n">
-        <v>91452</v>
+        <v>57789</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549277</v>
+        <v>549368</v>
       </c>
       <c r="R35" t="n">
-        <v>7132488</v>
+        <v>7132332</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494286</v>
+        <v>128494270</v>
       </c>
       <c r="B19" t="n">
-        <v>91470</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549350</v>
+        <v>549423</v>
       </c>
       <c r="R19" t="n">
-        <v>7132364</v>
+        <v>7132236</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2492,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494270</v>
+        <v>128494286</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>91470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,21 +2534,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549423</v>
+        <v>549350</v>
       </c>
       <c r="R20" t="n">
-        <v>7132236</v>
+        <v>7132364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2589,11 +2594,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128494269</v>
+        <v>128494266</v>
       </c>
       <c r="B22" t="n">
         <v>57685</v>
@@ -2757,22 +2757,22 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>549355</v>
+        <v>549449</v>
       </c>
       <c r="R22" t="n">
-        <v>7132343</v>
+        <v>7132219</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2824,7 +2824,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128494266</v>
+        <v>128494269</v>
       </c>
       <c r="B23" t="n">
         <v>57685</v>
@@ -2859,22 +2859,22 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>549449</v>
+        <v>549355</v>
       </c>
       <c r="R23" t="n">
-        <v>7132219</v>
+        <v>7132343</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128494294</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128494276</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>128494278</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128494289</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B9" t="n">
-        <v>91448</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R9" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>91454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R10" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,11 +1599,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
         <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>128494267</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>128494292</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>128494268</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494277</v>
+        <v>128494286</v>
       </c>
       <c r="B17" t="n">
-        <v>91748</v>
+        <v>91476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549287</v>
+        <v>549350</v>
       </c>
       <c r="R17" t="n">
-        <v>7132486</v>
+        <v>7132364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>88853</v>
+        <v>88859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494270</v>
+        <v>128494277</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>91754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549423</v>
+        <v>549287</v>
       </c>
       <c r="R19" t="n">
-        <v>7132236</v>
+        <v>7132486</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,11 +2492,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494286</v>
+        <v>128494274</v>
       </c>
       <c r="B20" t="n">
-        <v>91470</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549350</v>
+        <v>549300</v>
       </c>
       <c r="R20" t="n">
-        <v>7132364</v>
+        <v>7132514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,6 +2589,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494274</v>
+        <v>128494270</v>
       </c>
       <c r="B21" t="n">
-        <v>57682</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549300</v>
+        <v>549423</v>
       </c>
       <c r="R21" t="n">
-        <v>7132514</v>
+        <v>7132236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,7 +2725,7 @@
         <v>128494266</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>128494269</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494261</v>
+        <v>128494301</v>
       </c>
       <c r="B24" t="n">
-        <v>91452</v>
+        <v>88859</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549301</v>
+        <v>549427</v>
       </c>
       <c r="R24" t="n">
-        <v>7132504</v>
+        <v>7132215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128494301</v>
+        <v>128494281</v>
       </c>
       <c r="B25" t="n">
-        <v>88853</v>
+        <v>91454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549427</v>
+        <v>549420</v>
       </c>
       <c r="R25" t="n">
-        <v>7132215</v>
+        <v>7132412</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494281</v>
+        <v>128494261</v>
       </c>
       <c r="B26" t="n">
-        <v>91448</v>
+        <v>91458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549420</v>
+        <v>549301</v>
       </c>
       <c r="R26" t="n">
-        <v>7132412</v>
+        <v>7132504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>128494263</v>
       </c>
       <c r="B27" t="n">
-        <v>92149</v>
+        <v>92155</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494291</v>
+        <v>128494287</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>91476</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549291</v>
+        <v>549058</v>
       </c>
       <c r="R28" t="n">
-        <v>7132495</v>
+        <v>7132030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,11 +3385,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3416,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3422,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R29" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3491,7 +3486,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3518,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494275</v>
+        <v>128494291</v>
       </c>
       <c r="B30" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549391</v>
+        <v>549291</v>
       </c>
       <c r="R30" t="n">
-        <v>7132312</v>
+        <v>7132495</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3593,7 +3588,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hack, ganska färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494287</v>
+        <v>128494296</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3655,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R31" t="n">
-        <v>7132030</v>
+        <v>7131952</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,7 +3720,7 @@
         <v>128494288</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128494293</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>128494262</v>
       </c>
       <c r="B34" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>128494280</v>
       </c>
       <c r="B35" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>128494279</v>
       </c>
       <c r="B36" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>91460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R9" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,11 +1497,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>91454</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R10" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,6 +1594,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R11" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R12" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,7 +2036,7 @@
         <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494286</v>
+        <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>91476</v>
+        <v>91760</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549350</v>
+        <v>549287</v>
       </c>
       <c r="R17" t="n">
-        <v>7132364</v>
+        <v>7132486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494277</v>
+        <v>128494286</v>
       </c>
       <c r="B19" t="n">
-        <v>91754</v>
+        <v>91482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549287</v>
+        <v>549350</v>
       </c>
       <c r="R19" t="n">
-        <v>7132486</v>
+        <v>7132364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494274</v>
+        <v>128494270</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549300</v>
+        <v>549423</v>
       </c>
       <c r="R20" t="n">
-        <v>7132514</v>
+        <v>7132236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494270</v>
+        <v>128494274</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549423</v>
+        <v>549300</v>
       </c>
       <c r="R21" t="n">
-        <v>7132236</v>
+        <v>7132514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,7 +2929,7 @@
         <v>128494301</v>
       </c>
       <c r="B24" t="n">
-        <v>88859</v>
+        <v>88865</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128494281</v>
       </c>
       <c r="B25" t="n">
-        <v>91454</v>
+        <v>91460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>128494261</v>
       </c>
       <c r="B26" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>128494263</v>
       </c>
       <c r="B27" t="n">
-        <v>92155</v>
+        <v>92161</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128494287</v>
       </c>
       <c r="B28" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3411,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494275</v>
+        <v>128494291</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3422,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549391</v>
+        <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7132312</v>
+        <v>7132495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Hack, ganska färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3513,7 +3513,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494291</v>
+        <v>128494296</v>
       </c>
       <c r="B30" t="n">
         <v>79087</v>
@@ -3551,7 +3551,7 @@
         <v>549291</v>
       </c>
       <c r="R30" t="n">
-        <v>7132495</v>
+        <v>7131952</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R31" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,45 +3717,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128494288</v>
+        <v>128494280</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>57793</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549222</v>
+        <v>549368</v>
       </c>
       <c r="R32" t="n">
-        <v>7132132</v>
+        <v>7132332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,11 +3800,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3819,10 +3826,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494293</v>
+        <v>128494262</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>91464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,21 +3837,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3854,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549367</v>
+        <v>549277</v>
       </c>
       <c r="R33" t="n">
-        <v>7132331</v>
+        <v>7132488</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3890,11 +3897,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3921,10 +3923,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494262</v>
+        <v>128494288</v>
       </c>
       <c r="B34" t="n">
-        <v>91458</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3932,21 +3934,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3956,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549277</v>
+        <v>549222</v>
       </c>
       <c r="R34" t="n">
-        <v>7132488</v>
+        <v>7132132</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,6 +3994,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4018,57 +4025,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494280</v>
+        <v>128494293</v>
       </c>
       <c r="B35" t="n">
-        <v>57793</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549368</v>
+        <v>549367</v>
       </c>
       <c r="R35" t="n">
-        <v>7132332</v>
+        <v>7132331</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4101,6 +4096,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R11" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R12" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494300</v>
+        <v>128494285</v>
       </c>
       <c r="B15" t="n">
-        <v>88865</v>
+        <v>91482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549429</v>
+        <v>549438</v>
       </c>
       <c r="R15" t="n">
-        <v>7132363</v>
+        <v>7132438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494285</v>
+        <v>128494300</v>
       </c>
       <c r="B16" t="n">
-        <v>91482</v>
+        <v>88865</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549438</v>
+        <v>549429</v>
       </c>
       <c r="R16" t="n">
-        <v>7132438</v>
+        <v>7132363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128494294</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>128494278</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128494289</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>128494292</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128494285</v>
+        <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>91482</v>
+        <v>88867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>549438</v>
+        <v>549429</v>
       </c>
       <c r="R15" t="n">
-        <v>7132438</v>
+        <v>7132363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128494300</v>
+        <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>88865</v>
+        <v>91484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>549429</v>
+        <v>549438</v>
       </c>
       <c r="R16" t="n">
-        <v>7132363</v>
+        <v>7132438</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494277</v>
+        <v>128494299</v>
       </c>
       <c r="B17" t="n">
-        <v>91760</v>
+        <v>88867</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549287</v>
+        <v>549452</v>
       </c>
       <c r="R17" t="n">
-        <v>7132486</v>
+        <v>7132213</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494299</v>
+        <v>128494277</v>
       </c>
       <c r="B18" t="n">
-        <v>88865</v>
+        <v>91762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549452</v>
+        <v>549287</v>
       </c>
       <c r="R18" t="n">
-        <v>7132213</v>
+        <v>7132486</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>128494286</v>
       </c>
       <c r="B19" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494270</v>
+        <v>128494274</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549423</v>
+        <v>549300</v>
       </c>
       <c r="R20" t="n">
-        <v>7132236</v>
+        <v>7132514</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494274</v>
+        <v>128494270</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549300</v>
+        <v>549423</v>
       </c>
       <c r="R21" t="n">
-        <v>7132514</v>
+        <v>7132236</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494301</v>
+        <v>128494263</v>
       </c>
       <c r="B24" t="n">
-        <v>88865</v>
+        <v>92163</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549427</v>
+        <v>549306</v>
       </c>
       <c r="R24" t="n">
-        <v>7132215</v>
+        <v>7131940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128494281</v>
+        <v>128494301</v>
       </c>
       <c r="B25" t="n">
-        <v>91460</v>
+        <v>88867</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549420</v>
+        <v>549427</v>
       </c>
       <c r="R25" t="n">
-        <v>7132412</v>
+        <v>7132215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494261</v>
+        <v>128494281</v>
       </c>
       <c r="B26" t="n">
-        <v>91464</v>
+        <v>91462</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549301</v>
+        <v>549420</v>
       </c>
       <c r="R26" t="n">
-        <v>7132504</v>
+        <v>7132412</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128494263</v>
+        <v>128494261</v>
       </c>
       <c r="B27" t="n">
-        <v>92161</v>
+        <v>91466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549306</v>
+        <v>549301</v>
       </c>
       <c r="R27" t="n">
-        <v>7131940</v>
+        <v>7132504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494287</v>
+        <v>128494291</v>
       </c>
       <c r="B28" t="n">
-        <v>91482</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R28" t="n">
-        <v>7132030</v>
+        <v>7132495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,6 +3385,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494291</v>
+        <v>128494287</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>91484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549291</v>
+        <v>549058</v>
       </c>
       <c r="R29" t="n">
-        <v>7132495</v>
+        <v>7132030</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3482,11 +3487,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R30" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3615,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494275</v>
+        <v>128494296</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549391</v>
+        <v>549291</v>
       </c>
       <c r="R31" t="n">
-        <v>7132312</v>
+        <v>7131952</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hack, ganska färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,57 +3717,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128494280</v>
+        <v>128494262</v>
       </c>
       <c r="B32" t="n">
-        <v>57793</v>
+        <v>91466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549368</v>
+        <v>549277</v>
       </c>
       <c r="R32" t="n">
-        <v>7132332</v>
+        <v>7132488</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3826,10 +3814,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494262</v>
+        <v>128494288</v>
       </c>
       <c r="B33" t="n">
-        <v>91464</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3837,21 +3825,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3861,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549277</v>
+        <v>549222</v>
       </c>
       <c r="R33" t="n">
-        <v>7132488</v>
+        <v>7132132</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,6 +3885,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3923,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494288</v>
+        <v>128494293</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549222</v>
+        <v>549367</v>
       </c>
       <c r="R34" t="n">
-        <v>7132132</v>
+        <v>7132331</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,45 +4018,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494293</v>
+        <v>128494280</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>57793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549367</v>
+        <v>549368</v>
       </c>
       <c r="R35" t="n">
-        <v>7132331</v>
+        <v>7132332</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,11 +4101,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4130,7 +4130,7 @@
         <v>128494279</v>
       </c>
       <c r="B36" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B9" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R9" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,6 +1497,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>91462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1534,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1558,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R10" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,11 +1599,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R11" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R12" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494299</v>
+        <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>88867</v>
+        <v>91762</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549452</v>
+        <v>549287</v>
       </c>
       <c r="R17" t="n">
-        <v>7132213</v>
+        <v>7132486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494277</v>
+        <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>91762</v>
+        <v>88867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549287</v>
+        <v>549452</v>
       </c>
       <c r="R18" t="n">
-        <v>7132486</v>
+        <v>7132213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494274</v>
+        <v>128494270</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549300</v>
+        <v>549423</v>
       </c>
       <c r="R20" t="n">
-        <v>7132514</v>
+        <v>7132236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494270</v>
+        <v>128494274</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549423</v>
+        <v>549300</v>
       </c>
       <c r="R21" t="n">
-        <v>7132236</v>
+        <v>7132514</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494287</v>
+        <v>128494296</v>
       </c>
       <c r="B29" t="n">
-        <v>91484</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7132030</v>
+        <v>7131952</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3487,6 +3487,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3615,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494296</v>
+        <v>128494287</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3631,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549291</v>
+        <v>549058</v>
       </c>
       <c r="R31" t="n">
-        <v>7131952</v>
+        <v>7132030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128494262</v>
+        <v>128494288</v>
       </c>
       <c r="B32" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549277</v>
+        <v>549222</v>
       </c>
       <c r="R32" t="n">
-        <v>7132488</v>
+        <v>7132132</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,6 +3788,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,7 +3819,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494288</v>
+        <v>128494293</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -3849,10 +3854,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549222</v>
+        <v>549367</v>
       </c>
       <c r="R33" t="n">
-        <v>7132132</v>
+        <v>7132331</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494293</v>
+        <v>128494262</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3927,21 +3932,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3951,10 +3956,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549367</v>
+        <v>549277</v>
       </c>
       <c r="R34" t="n">
-        <v>7132331</v>
+        <v>7132488</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3987,11 +3992,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R11" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R12" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3717,10 +3717,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128494288</v>
+        <v>128494262</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>91466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>549222</v>
+        <v>549277</v>
       </c>
       <c r="R32" t="n">
-        <v>7132132</v>
+        <v>7132488</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3788,11 +3788,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3819,7 +3814,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494293</v>
+        <v>128494288</v>
       </c>
       <c r="B33" t="n">
         <v>79089</v>
@@ -3854,10 +3849,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549367</v>
+        <v>549222</v>
       </c>
       <c r="R33" t="n">
-        <v>7132331</v>
+        <v>7132132</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3921,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494262</v>
+        <v>128494293</v>
       </c>
       <c r="B34" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3932,21 +3927,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3956,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549277</v>
+        <v>549367</v>
       </c>
       <c r="R34" t="n">
-        <v>7132488</v>
+        <v>7132331</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,6 +3987,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128494290</v>
+        <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>91463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>549409</v>
+        <v>549266</v>
       </c>
       <c r="R9" t="n">
-        <v>7132455</v>
+        <v>7132443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,11 +1497,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128494282</v>
+        <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>91462</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1539,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>549266</v>
+        <v>549409</v>
       </c>
       <c r="R10" t="n">
-        <v>7132443</v>
+        <v>7132455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,6 +1594,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R11" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R12" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2133,7 +2133,7 @@
         <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494299</v>
+        <v>128494286</v>
       </c>
       <c r="B18" t="n">
-        <v>88867</v>
+        <v>91485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549452</v>
+        <v>549350</v>
       </c>
       <c r="R18" t="n">
-        <v>7132213</v>
+        <v>7132364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494286</v>
+        <v>128494274</v>
       </c>
       <c r="B19" t="n">
-        <v>91484</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549350</v>
+        <v>549300</v>
       </c>
       <c r="R19" t="n">
-        <v>7132364</v>
+        <v>7132514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,6 +2492,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494274</v>
+        <v>128494299</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>88867</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,21 +2636,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,22 +2660,22 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549300</v>
+        <v>549452</v>
       </c>
       <c r="R21" t="n">
-        <v>7132514</v>
+        <v>7132213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2680,7 +2685,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2691,11 +2696,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494263</v>
+        <v>128494301</v>
       </c>
       <c r="B24" t="n">
-        <v>92163</v>
+        <v>88867</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549306</v>
+        <v>549427</v>
       </c>
       <c r="R24" t="n">
-        <v>7131940</v>
+        <v>7132215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128494301</v>
+        <v>128494281</v>
       </c>
       <c r="B25" t="n">
-        <v>88867</v>
+        <v>91463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549427</v>
+        <v>549420</v>
       </c>
       <c r="R25" t="n">
-        <v>7132215</v>
+        <v>7132412</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494281</v>
+        <v>128494261</v>
       </c>
       <c r="B26" t="n">
-        <v>91462</v>
+        <v>91467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549420</v>
+        <v>549301</v>
       </c>
       <c r="R26" t="n">
-        <v>7132412</v>
+        <v>7132504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128494261</v>
+        <v>128494263</v>
       </c>
       <c r="B27" t="n">
-        <v>91466</v>
+        <v>92164</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549301</v>
+        <v>549306</v>
       </c>
       <c r="R27" t="n">
-        <v>7132504</v>
+        <v>7131940</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494275</v>
+        <v>128494287</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549391</v>
+        <v>549058</v>
       </c>
       <c r="R30" t="n">
-        <v>7132312</v>
+        <v>7132030</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,11 +3589,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3620,10 +3615,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494287</v>
+        <v>128494275</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>57686</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3631,21 +3626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3655,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549058</v>
+        <v>549391</v>
       </c>
       <c r="R31" t="n">
-        <v>7132030</v>
+        <v>7132312</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,7 +3720,7 @@
         <v>128494262</v>
       </c>
       <c r="B32" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128494294</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128494276</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>128494278</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128494289</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>128494267</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>128494295</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>128494292</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>128494268</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>88867</v>
+        <v>88894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494286</v>
+        <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>91485</v>
+        <v>88894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549350</v>
+        <v>549452</v>
       </c>
       <c r="R18" t="n">
-        <v>7132364</v>
+        <v>7132213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>128494274</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>128494270</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494299</v>
+        <v>128494286</v>
       </c>
       <c r="B21" t="n">
-        <v>88867</v>
+        <v>91512</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,22 +2660,22 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549452</v>
+        <v>549350</v>
       </c>
       <c r="R21" t="n">
-        <v>7132213</v>
+        <v>7132364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2725,7 +2725,7 @@
         <v>128494266</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>128494269</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494301</v>
+        <v>128494263</v>
       </c>
       <c r="B24" t="n">
-        <v>88867</v>
+        <v>92191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549427</v>
+        <v>549306</v>
       </c>
       <c r="R24" t="n">
-        <v>7132215</v>
+        <v>7131940</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
         <v>128494281</v>
       </c>
       <c r="B25" t="n">
-        <v>91463</v>
+        <v>91490</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494261</v>
+        <v>128494301</v>
       </c>
       <c r="B26" t="n">
-        <v>91467</v>
+        <v>88894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549301</v>
+        <v>549427</v>
       </c>
       <c r="R26" t="n">
-        <v>7132504</v>
+        <v>7132215</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128494263</v>
+        <v>128494261</v>
       </c>
       <c r="B27" t="n">
-        <v>92164</v>
+        <v>91494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>549306</v>
+        <v>549301</v>
       </c>
       <c r="R27" t="n">
-        <v>7131940</v>
+        <v>7132504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494291</v>
+        <v>128494287</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>91512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549291</v>
+        <v>549058</v>
       </c>
       <c r="R28" t="n">
-        <v>7132495</v>
+        <v>7132030</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,11 +3385,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3416,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494296</v>
+        <v>128494291</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7131952</v>
+        <v>7132495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494287</v>
+        <v>128494296</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3553,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R30" t="n">
-        <v>7132030</v>
+        <v>7131952</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,6 +3584,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,7 +3618,7 @@
         <v>128494275</v>
       </c>
       <c r="B31" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128494262</v>
       </c>
       <c r="B32" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128494288</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>128494293</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>128494280</v>
       </c>
       <c r="B35" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>128494279</v>
       </c>
       <c r="B36" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R11" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R12" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494277</v>
+        <v>128494274</v>
       </c>
       <c r="B17" t="n">
-        <v>91790</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549287</v>
+        <v>549300</v>
       </c>
       <c r="R17" t="n">
-        <v>7132486</v>
+        <v>7132514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,6 +2298,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494299</v>
+        <v>128494270</v>
       </c>
       <c r="B18" t="n">
-        <v>88894</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2359,22 +2364,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549452</v>
+        <v>549423</v>
       </c>
       <c r="R18" t="n">
-        <v>7132213</v>
+        <v>7132236</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2384,7 +2389,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2395,6 +2400,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494274</v>
+        <v>128494286</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>91512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,21 +2442,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2456,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549300</v>
+        <v>549350</v>
       </c>
       <c r="R19" t="n">
-        <v>7132514</v>
+        <v>7132364</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2492,11 +2502,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2523,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494270</v>
+        <v>128494277</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>91790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,21 +2539,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2558,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549423</v>
+        <v>549287</v>
       </c>
       <c r="R20" t="n">
-        <v>7132236</v>
+        <v>7132486</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2594,11 +2599,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494286</v>
+        <v>128494299</v>
       </c>
       <c r="B21" t="n">
-        <v>91512</v>
+        <v>88894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,22 +2660,22 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549350</v>
+        <v>549452</v>
       </c>
       <c r="R21" t="n">
-        <v>7132364</v>
+        <v>7132213</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3814,45 +3814,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494288</v>
+        <v>128494280</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>57820</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549222</v>
+        <v>549368</v>
       </c>
       <c r="R33" t="n">
-        <v>7132132</v>
+        <v>7132332</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,11 +3897,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,7 +3923,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494293</v>
+        <v>128494288</v>
       </c>
       <c r="B34" t="n">
         <v>79116</v>
@@ -3951,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549367</v>
+        <v>549222</v>
       </c>
       <c r="R34" t="n">
-        <v>7132331</v>
+        <v>7132132</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,57 +4025,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494280</v>
+        <v>128494293</v>
       </c>
       <c r="B35" t="n">
-        <v>57820</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549368</v>
+        <v>549367</v>
       </c>
       <c r="R35" t="n">
-        <v>7132332</v>
+        <v>7132331</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4101,6 +4096,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 60327-2023 artfynd.xlsx
+++ b/artfynd/A 60327-2023 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>128494294</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>128494278</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>128494289</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128494282</v>
       </c>
       <c r="B9" t="n">
-        <v>91490</v>
+        <v>91495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>128494290</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128494295</v>
+        <v>128494267</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,22 +1660,22 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>549282</v>
+        <v>549449</v>
       </c>
       <c r="R11" t="n">
-        <v>7132002</v>
+        <v>7132243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128494267</v>
+        <v>128494295</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,22 +1762,22 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>549449</v>
+        <v>549282</v>
       </c>
       <c r="R12" t="n">
-        <v>7132243</v>
+        <v>7132002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1832,7 @@
         <v>128494292</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128494300</v>
       </c>
       <c r="B15" t="n">
-        <v>88894</v>
+        <v>88899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128494285</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128494274</v>
+        <v>128494277</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>91795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>549300</v>
+        <v>549287</v>
       </c>
       <c r="R17" t="n">
-        <v>7132514</v>
+        <v>7132486</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,11 +2298,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,10 +2324,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128494270</v>
+        <v>128494299</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>88899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,21 +2335,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,22 +2359,22 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>549423</v>
+        <v>549452</v>
       </c>
       <c r="R18" t="n">
-        <v>7132236</v>
+        <v>7132213</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Jämtland</t>
+          <t>Västerbotten</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Strömsund</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2389,7 +2384,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Tåsjö</t>
+          <t>Dorotea</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2400,11 +2395,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2431,10 +2421,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128494286</v>
+        <v>128494274</v>
       </c>
       <c r="B19" t="n">
-        <v>91512</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,21 +2432,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2456,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>549350</v>
+        <v>549300</v>
       </c>
       <c r="R19" t="n">
-        <v>7132364</v>
+        <v>7132514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,6 +2492,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128494277</v>
+        <v>128494270</v>
       </c>
       <c r="B20" t="n">
-        <v>91790</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,21 +2534,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2563,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>549287</v>
+        <v>549423</v>
       </c>
       <c r="R20" t="n">
-        <v>7132486</v>
+        <v>7132236</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,6 +2594,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128494299</v>
+        <v>128494286</v>
       </c>
       <c r="B21" t="n">
-        <v>88894</v>
+        <v>91517</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,21 +2636,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,22 +2660,22 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>549452</v>
+        <v>549350</v>
       </c>
       <c r="R21" t="n">
-        <v>7132213</v>
+        <v>7132364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Västerbotten</t>
+          <t>Jämtland</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Strömsund</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Dorotea</t>
+          <t>Tåsjö</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2926,32 +2926,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128494263</v>
+        <v>128494301</v>
       </c>
       <c r="B24" t="n">
-        <v>92191</v>
+        <v>88899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>549306</v>
+        <v>549427</v>
       </c>
       <c r="R24" t="n">
-        <v>7131940</v>
+        <v>7132215</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,32 +3023,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128494281</v>
+        <v>128494263</v>
       </c>
       <c r="B25" t="n">
-        <v>91490</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>549420</v>
+        <v>549306</v>
       </c>
       <c r="R25" t="n">
-        <v>7132412</v>
+        <v>7131940</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128494301</v>
+        <v>128494281</v>
       </c>
       <c r="B26" t="n">
-        <v>88894</v>
+        <v>91495</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>549427</v>
+        <v>549420</v>
       </c>
       <c r="R26" t="n">
-        <v>7132215</v>
+        <v>7132412</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,7 +3220,7 @@
         <v>128494261</v>
       </c>
       <c r="B27" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128494287</v>
+        <v>128494291</v>
       </c>
       <c r="B28" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>549058</v>
+        <v>549291</v>
       </c>
       <c r="R28" t="n">
-        <v>7132030</v>
+        <v>7132495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,6 +3385,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128494291</v>
+        <v>128494296</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3449,7 +3454,7 @@
         <v>549291</v>
       </c>
       <c r="R29" t="n">
-        <v>7132495</v>
+        <v>7131952</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128494296</v>
+        <v>128494275</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3529,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>549291</v>
+        <v>549391</v>
       </c>
       <c r="R30" t="n">
-        <v>7131952</v>
+        <v>7132312</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3588,7 +3593,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3615,10 +3620,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128494275</v>
+        <v>128494287</v>
       </c>
       <c r="B31" t="n">
-        <v>57713</v>
+        <v>91517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3631,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>549391</v>
+        <v>549058</v>
       </c>
       <c r="R31" t="n">
-        <v>7132312</v>
+        <v>7132030</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack, ganska färska</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3720,7 +3720,7 @@
         <v>128494262</v>
       </c>
       <c r="B32" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,57 +3814,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128494280</v>
+        <v>128494288</v>
       </c>
       <c r="B33" t="n">
-        <v>57820</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>549368</v>
+        <v>549222</v>
       </c>
       <c r="R33" t="n">
-        <v>7132332</v>
+        <v>7132132</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3897,6 +3885,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3923,10 +3916,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128494288</v>
+        <v>128494293</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3958,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>549222</v>
+        <v>549367</v>
       </c>
       <c r="R34" t="n">
-        <v>7132132</v>
+        <v>7132331</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,45 +4018,57 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128494293</v>
+        <v>128494280</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>57820</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Frostberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>549367</v>
+        <v>549368</v>
       </c>
       <c r="R35" t="n">
-        <v>7132331</v>
+        <v>7132332</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4096,11 +4101,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4130,7 +4130,7 @@
         <v>128494279</v>
       </c>
       <c r="B36" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>128494284</v>
       </c>
       <c r="B37" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
